--- a/docs/requirements/VOSS_개발일정.xlsx
+++ b/docs/requirements/VOSS_개발일정.xlsx
@@ -4059,7 +4059,7 @@
       </c>
       <c r="H37" s="48" t="inlineStr">
         <is>
-          <t>move_line 큐 30분 무정지 (10/08 PL 승인, 원래 1시간)</t>
+          <t>move_line 큐 30분 무정지 (10/09 PL 승인(#123 리뷰), 원래 1시간 — 1시간 연속은 G1 세션 gateway 로그(#121 빌드, 60분·FAULT 0), 미달 시 추가 soak)</t>
         </is>
       </c>
       <c r="I37" s="48" t="inlineStr">

--- a/docs/requirements/VOSS_개발일정.xlsx
+++ b/docs/requirements/VOSS_개발일정.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="412">
   <si>
     <r>
       <rPr>
@@ -55,2549 +55,2706 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">· 2026-10-05 ~ 10-16 (v1.4: Sprint 1 ~10/11, Sprint 2 10/12~14)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">상태 열은 드롭다운(예정/진행/완료/지연), 진행률 열은 드롭다운(시작전/진행중/완료)으로 고른다. 시작·종료 날짜를 바꾸면 간트 막대가 따라 움직임. 노란 셀이 입력 칸.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">파트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">담당</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시작</t>
-  </si>
-  <si>
-    <t xml:space="preserve">종료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">일수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">완료 기준 / 산출물</t>
-  </si>
-  <si>
-    <t xml:space="preserve">관련 요구사항</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상태</t>
-  </si>
-  <si>
-    <t xml:space="preserve">진행률</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요일 / 비고</t>
-  </si>
-  <si>
-    <t xml:space="preserve">휴무</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">휴무(한글날)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">토</t>
-  </si>
-  <si>
-    <t xml:space="preserve">일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">월</t>
-  </si>
-  <si>
-    <t xml:space="preserve">금</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">인터페이스 확정: 노드·토픽·intent JSON·voss_config.yaml 형식, 레포 생성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레포에 인터페이스 문서 커밋</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SRD 9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, BRD 8.3</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">예정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시작전</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/06 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실측</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실측 체크리스트 시트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">체크리스트 전 항목 기록</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SRD 16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">T03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">중간 점검 발표 준비·발표 (주제·진행 방향·진행률)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">발표 완료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRD 8.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T04</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게이트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">추종 파지 성공률 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">70% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">판단</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미달 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개루프 전환</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">성공률 로그, 결정 기록</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-04, BRD 8.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체 루프 리허설 (박스 10개 8단계 대본)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">리허설 로그, NFR-01~03 실측값</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRD 8.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">최종 리허설·시연 영상 촬영·시연</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 이상 적재</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-NF-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">발표 자료(PPT) 마무리·발표</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRD 8.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">음성·웹·HMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정의석</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">voice_listener: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">호출어 검출 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ Whisper </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">STT</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">녹음 파일 20개 전사 ≥ 90%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-13, SR-SW-10·11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T09</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">intent_parser: LangChain·OpenAI intent JSON + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">허용 목록 검증</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">지시 20개 중 19개 정확</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-14, SR-SW-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T10</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">speech_out: TTS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">엔진 선정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연동</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">발화 → 응답 ≤ 3초</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-SW-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T11</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mosquitto </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">브로커</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·hmi_bridge, MQTT JSON </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">스키마 확정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">voss/state·command </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">왕복 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-SW-16, SR-IF-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T12</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sort_logger·DB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">컨테이너 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(DB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종류 결정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">결과 토픽 1건 → DB 1행</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-20, SR-SW-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">웹 HMI: 운전·분류 버튼, 투입 수량, 집계, 보류 목록, OCR 결과, 로봇 상태</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HMI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">반영 ≤ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">초</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-19, SR-SW-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체 루프 연동: 음성 → sort_manager → TTS·HMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">지시 4종 각 1회 동작</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">예외 처리·소음 대응·HMI 폴백 점검, 리허설</t>
-  </si>
-  <si>
-    <t xml:space="preserve">리허설 통과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-09, R-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">비전·OCR·통합</t>
-  </si>
-  <si>
-    <t xml:space="preserve">남현지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">핸드아이 캘리브레이션 (로봇 제어와 함께)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">검증점 오차 ≤ 5 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">박스 검출: 데이터 촬영·YOLO 학습 또는 세그멘테이션, box_tracker 30 Hz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">검출률 ≥ 99%, 지연 ≤ 100 ms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-01, SR-SW-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">송장 샘플 OCR 검증 (PaddleOCR, 전처리, 퍼지 매칭)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정지 송장 50장 ≥ 95%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-SW-08·09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T19</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">label_reader: 1·2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OCR, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">선명 프레임 선택</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다수결</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">추종 중 50장 ≥ 90%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-08~11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T20</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sort_manager FSM·voss_config.yaml·zone_map </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">토픽</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상태 전이 단독 시험 통과</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-SW-14·15, SR-IF-02~04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">추종·파지 지원 (탐지 접점, 지연 오프셋 보정)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">게이트 성공률 측정 참여</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-05, R-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">비전 컨테이너 구성 (GPU, 마운트), 전체 루프 통합 (v1.4: 10/11 통합에 포함)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">스크립트 1회 기동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-21, SR-SW-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">김학민·정의석 (인계)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">재확인·질문·보류 흐름, 로그·성공률 집계, 시연 대본 → 인계 S2-T12·T19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">흐린 송장 박스 완주 3회</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-12, SR-NF-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">박병후·김학민 (인계)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">리허설·튜닝 → 인계 S2-T11·T12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">추종·파지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">박병후</t>
-  </si>
-  <si>
-    <t xml:space="preserve">서보 스트리밍 토픽 확인 (dsr_msgs2), 제어 방식 결정</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">servol_stream </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유무 기록</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-SW-04, SR-IF-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">개루프 동기 추종 (벨트 속도 피드포워드) 베이스라인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">벨트 위 박스 파지 1회 성공</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T27</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">belt_servo: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">폐루프 서보 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">픽셀 오차 → 속도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하강</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파지 타이밍</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">추종 파지 성공률 ≥ 70% (20회)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-03, SR-NF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">서보 안정화, 파지 실패 감지·재시도, 2단계 OCR 프레임 연동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">재시도 포함 성공률 유지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-05, SR-FN-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">타이밍 튜닝·리허설</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-NF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">로봇 제어·환경 설정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">김학민</t>
-  </si>
-  <si>
-    <t xml:space="preserve">벨트 속도 실측·아두이노 설정값 표, 10 cm/s 이하 설정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">설정값-속도 표</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-HW-04·05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업대 치수·5구역 좌표 실측·등록, 컨트롤러·PC 사양 확인</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">voss_config.yaml </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">좌표 입력</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-HW-08·09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">두산 브링업·robot_gateway 단일 호출 큐·툴/TCP 등록 스크립트</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">move_line </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">큐 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분 무정지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10/09 PL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">승인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(#123 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">리뷰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원래 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시간 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시간 연속은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">세션 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">gateway </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(#121 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빌드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·FAULT 0), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미달 시 추가 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">soak)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-SW-04, SR-IF-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">송장 제작·인쇄·부착 (10매 + 흐린 1), 카메라 노출·조명 세팅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">송장 세트 완성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-HW-07, SR-NF-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T34</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RG2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제어 경로 결정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파지력 설정 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종이 박스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">찌그러짐 없는 파지 10회</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-HW-02, SR-SW-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정지 Pick and Place: move_to_zone, 격자 오프셋, 복귀</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구역 적재 각 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회 성공</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-06, SR-IF-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적재 시퀀스 통합, 직접교시 teach_zone (Should)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체 루프에서 적재 동작</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">리허설 지원·환경 재점검</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-NF-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/13 18:00 Sprint 2 게이트 (팔레타이징 3개 동 완주, 음성 기동 1회 성공)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시연 포함 여부 결정 기록</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRD v1.4 10.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T09</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">음성 기동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] voss_launcher </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">음성 시스템 기동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종료</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">기동 3/3, 3분 이내, 종료 3회</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-VOICE-11~16, NFR-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정의석·김학민</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">음성 기동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기동 프로필 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(g0-runbook → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">준비 확인 스크립트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">스크립트만으로 수동 기동과 같은 상태</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-VOICE-13·16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T19</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인계 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">T23] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">성공률 집계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 10/14 NFR-01~03 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실측값 보고</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-01~03 실측값 표 PR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-01~03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[팔레타이징] Sprint 2 인터페이스 변경안 (docs/interfaces + voss_msgs 한 PR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">interface PR 머지, 전체 빌드 통과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRD v1.4 10.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[팔레타이징] 배치 계획 순수 함수 pallet_plan + 단위 시험</t>
-  </si>
-  <si>
-    <t xml:space="preserve">단위 시험 통과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-PAL-03·04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[팔레타이징] sort_manager PALLETIZING 상태·palletize 명령·멈춤/재개</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1개 동 → 3개 동 경로 실기 완주</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-PAL-02·05·06·08·10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[팔레타이징] 음성 palletize intent (route)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">palletize 5문장 중 5 정확</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-PAL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[팔레타이징] 기록: SortResult.slot, pallet_log, ListPlacements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PalletResult 1건 → pallet_log 1행</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-PAL-03·09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[팔레타이징] HMI 경로 입력·진행률·팔레트 배치도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HMI 버튼으로 1회 완주, 반영 ≤ 1초</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-PAL-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[PL] 시연 단계 0·9 문안, 박스 구성 결정, 게이트 판정·문서 갱신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대본 반영, 게이트 결정 기록</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRD v1.4 10.8·10.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[고도화·3순위] BoxTrack yaw 관측 + J6 회전 시 핸드아이 오차 측정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0·15·30·45° yaw 오차 기록, interface PR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-SERVO-04·06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[인계 T24] 리허설 중 검출·OCR 튜닝, 비전 이슈 1차 대응</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OCR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실패 원인 표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">리허설 통과</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[고도화·3순위] 하강·들기 사다리꼴 속도 프로파일</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시뮬 통과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실기 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수준 유지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계별 시간 표</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-SERVO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[고도화·3순위] 온라인 벨트 속도 추정 (직선 맞춤, 단계 적용)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 로그 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회 ② 정확도 보고 ③ 적용 여부 결정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-SERVO-02·03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[고도화·3순위] J6 회전 파지 (TRACK 초반 회전, LIFT 원위치)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계별 결과 기록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시연 장면 포함 여부 결정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-SERVO-05·07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">김학민·남현지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">팔레트 구역 좌표 교시·9칸 ikin 도달성, 베이스 위치 재측정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9칸 ikin 해 또는 대안 배치, measurements PR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-PAL-06·07, R-18~21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MoveToZone PICK(10/13→10/12)·DROP·PALLET 칸 계산·관절 경유점</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A·B·C PICK 10회, 팔레트 9칸 DROP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-PAL-05~07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[인계 T23·T24] 재확인 흐름 실기(흐린 송장 완주 3회), 시연 대본 운영, 리허설 진행·판정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">흐린 송장 완주 3회, 회차별 판정 기록</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-OCR-06·07, NFR-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2-T17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[고도화·3순위] gateway 회전 가속·각속도, 에뮬레이터 확인, 그리퍼-벨트 프레임 간섭 측정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">에뮬레이터·간섭 측정 기록</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR-SERVO-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">파트별 진행률</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업 수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">완료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">진행</t>
-  </si>
-  <si>
-    <t xml:space="preserve">지연</t>
-  </si>
-  <si>
-    <t xml:space="preserve">완료율 (진행률=완료)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범례: 회색 날짜 = 휴무(10/5·10/9)·주말(10/10·11, 강의실 사용 가능). 막대 색 = 파트. 출처: VOSS BRD 6.3·6.4, SRD 16장 (2026-10-05). v1.4(2026-10-12): S2-TXX = Sprint 2 작업(BRD v1.4 10장, 이슈 초안과 같은 번호), T22 를 10/11 로 당김, T23·T24 인계.</t>
-  </si>
-  <si>
+      <t xml:space="preserve">· 2026-10-05 ~ 10-16 (v1.5: Sprint 1 ~10/11, Sprint 2 10/12~14, </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VOSS </t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">팔레트 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마일스톤</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">날짜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">마일스톤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">통과 기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">관련</t>
-  </si>
-  <si>
-    <t xml:space="preserve">인터페이스 확정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">노드·토픽·서비스 이름, intent JSON, voss_config.yaml 형식을 레포에 커밋</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SRD 9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">실측·확인 완료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">벨트 속도표, 작업대 좌표, 컨트롤러 버전, 서보 토픽 유무, RG2 경로, GPU 사양, 캘리브레이션 기록</t>
-  </si>
-  <si>
-    <t xml:space="preserve">중간 점검 발표</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주제·진행 방향·진행률 설명 완료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정지 Pick and Place 동작</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-06</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게이트</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">추종 파지 성공률 ≥ 70% (20회). 미달 시 B 개루프 동기 추종 전환 또는 범위 축소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체 루프 통합 (v1.4: 10/13 → 10/11, 남현지) · Sprint 1 마감</t>
-  </si>
-  <si>
-    <t xml:space="preserve">음성 → 판독 → 파지 → 적재 → HMI·DB 한 번에 완주</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-FN-15·20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 2 게이트 (18:00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">팔레타이징 3개 동 경로 실기 1회 완주, 음성 시스템 기동 실기 1회 성공. 미달 기능은 시연 제외</t>
-  </si>
-  <si>
-    <t xml:space="preserve">파트별 역할 완료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">리허설 로그로 NFR-01~03 실측값 확보 (v1.4: 남현지 몫 T23·T24 인계, NFR 보고 정의석)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시연</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">박스 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계 대본 완주</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 이상 올바른 구역 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ v1.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단계 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">음성 기동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·9(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">팔레타이징</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게이트 통과 시</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-NF-06, BRD 8.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">발표</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PPT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">발표 완료</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/06 </t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">칸</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실측</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">박스 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
         <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">상태 열은 드롭다운(예정/진행/완료/지연), 진행률 열은 드롭다운(시작전/진행중/완료)으로 고른다. 시작·종료 날짜를 바꾸면 간트 막대가 따라 움직임. 노란 셀이 입력 칸.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">담당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">종료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">완료 기준 / 산출물</t>
+  </si>
+  <si>
+    <t xml:space="preserve">관련 요구사항</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">진행률</t>
+  </si>
+  <si>
+    <t xml:space="preserve">요일 / 비고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">휴무</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">휴무(한글날)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">토</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인터페이스 확정: 노드·토픽·intent JSON·voss_config.yaml 형식, 레포 생성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레포에 인터페이스 문서 커밋</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SRD 9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, BRD 8.3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">예정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작전</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실측 체크리스트 시트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">체크리스트 전 항목 기록</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SRD 16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">중간 점검 발표 준비·발표 (주제·진행 방향·진행률)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">발표 완료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRD 8.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게이트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추종 파지 성공률 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미달 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개루프 전환</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">성공률 로그, 결정 기록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-04, BRD 8.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체 루프 리허설 (박스 10개 8단계 대본)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리허설 로그, NFR-01~03 실측값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRD 8.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최종 리허설·시연 영상 촬영·시연</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 이상 적재</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-NF-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">발표 자료(PPT) 마무리·발표</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRD 8.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">음성·웹·HMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정의석</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">voice_listener: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">호출어 검출 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ Whisper </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STT</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">녹음 파일 20개 전사 ≥ 90%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-13, SR-SW-10·11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T09</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">intent_parser: LangChain·OpenAI intent JSON + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">허용 목록 검증</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">지시 20개 중 19개 정확</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-14, SR-SW-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">speech_out: TTS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">엔진 선정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">발화 → 응답 ≤ 3초</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-SW-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T11</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mosquitto </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">브로커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·hmi_bridge, MQTT JSON </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스키마 확정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">voss/state·command </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">왕복 확인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-SW-16, SR-IF-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T12</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sort_logger·DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">컨테이너 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종류 결정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">결과 토픽 1건 → DB 1행</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-20, SR-SW-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">웹 HMI: 운전·분류 버튼, 투입 수량, 집계, 보류 목록, OCR 결과, 로봇 상태</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HMI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반영 ≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">초</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-19, SR-SW-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체 루프 연동: 음성 → sort_manager → TTS·HMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지시 4종 각 1회 동작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예외 처리·소음 대응·HMI 폴백 점검, 리허설</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리허설 통과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-09, R-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비전·OCR·통합</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남현지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">핸드아이 캘리브레이션 (로봇 제어와 함께)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">검증점 오차 ≤ 5 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">박스 검출: 데이터 촬영·YOLO 학습 또는 세그멘테이션, box_tracker 30 Hz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">검출률 ≥ 99%, 지연 ≤ 100 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-01, SR-SW-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">송장 샘플 OCR 검증 (PaddleOCR, 전처리, 퍼지 매칭)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정지 송장 50장 ≥ 95%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-SW-08·09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T19</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">label_reader: 1·2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OCR, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선명 프레임 선택</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다수결</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">추종 중 50장 ≥ 90%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-08~11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T20</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sort_manager FSM·voss_config.yaml·zone_map </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">토픽</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상태 전이 단독 시험 통과</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-SW-14·15, SR-IF-02~04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추종·파지 지원 (탐지 접점, 지연 오프셋 보정)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">게이트 성공률 측정 참여</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-05, R-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비전 컨테이너 구성 (GPU, 마운트), 전체 루프 통합 (v1.4: 10/11 통합에 포함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스크립트 1회 기동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-21, SR-SW-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">김학민·정의석 (인계)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">재확인·질문·보류 흐름, 로그·성공률 집계, 시연 대본 → 인계 S2-T12·T19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">흐린 송장 박스 완주 3회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-12, SR-NF-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">박병후·김학민 (인계)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리허설·튜닝 → 인계 S2-T11·T12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추종·파지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">박병후</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서보 스트리밍 토픽 확인 (dsr_msgs2), 제어 방식 결정</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">servol_stream </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유무 기록</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-SW-04, SR-IF-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">개루프 동기 추종 (벨트 속도 피드포워드) 베이스라인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">벨트 위 박스 파지 1회 성공</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">belt_servo: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폐루프 서보 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">픽셀 오차 → 속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하강</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파지 타이밍</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">추종 파지 성공률 ≥ 70% (20회)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-03, SR-NF-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서보 안정화, 파지 실패 감지·재시도, 2단계 OCR 프레임 연동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">재시도 포함 성공률 유지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-05, SR-FN-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">타이밍 튜닝·리허설</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-NF-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로봇 제어·환경 설정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">김학민</t>
+  </si>
+  <si>
+    <t xml:space="preserve">벨트 속도 실측·아두이노 설정값 표, 10 cm/s 이하 설정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">설정값-속도 표</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-HW-04·05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업대 치수·5구역 좌표 실측·등록, 컨트롤러·PC 사양 확인</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">voss_config.yaml </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">좌표 입력</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-HW-08·09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">두산 브링업·robot_gateway 단일 호출 큐·툴/TCP 등록 스크립트</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">move_line </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">큐 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분 무정지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10/09 PL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">승인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(#123 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리뷰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원래 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시간 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시간 연속은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세션 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">gateway </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(#121 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빌드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·FAULT 0), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미달 시 추가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">soak)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-SW-04, SR-IF-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">송장 제작·인쇄·부착 (10매 + 흐린 1), 카메라 노출·조명 세팅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">송장 세트 완성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-HW-07, SR-NF-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T34</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RG2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제어 경로 결정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파지력 설정 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종이 박스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">찌그러짐 없는 파지 10회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-HW-02, SR-SW-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정지 Pick and Place: move_to_zone, 격자 오프셋, 복귀</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구역 적재 각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회 성공</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-06, SR-IF-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적재 시퀀스 통합, 직접교시 teach_zone (Should)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체 루프에서 적재 동작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리허설 지원·환경 재점검</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-NF-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/13 18:00 Sprint 2 게이트 (팔레타이징 기준은 결정 D3, 음성 기동 1회 성공)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시연 포함 여부 결정 기록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRD v1.5 10.2, D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T09</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">음성 기동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] voss_launcher </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">음성 시스템 기동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종료</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">기동 3/3, 3분 이내, 종료 3회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-VOICE-11~16, NFR-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정의석·김학민</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">음성 기동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기동 프로필 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(g0-runbook → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">준비 확인 스크립트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">스크립트만으로 수동 기동과 같은 상태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-VOICE-13·16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T19</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T23] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성공률 집계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 10/14 NFR-01~03 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실측값 보고</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-01~03 실측값 표 PR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-01~03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T22</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">투입 예정 수량 기본 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20, "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">몇 개 남았어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">?"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 팔레타이징 결과 반영</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S1 적재 후 남은 수 답 일치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-PAL-12, TR-VOICE-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[팔레타이징] Sprint 2 인터페이스 변경안 v1.5 (slot 0~15, PalletResult OVERFLOW·EXCLUDED, docs/interfaces + voss_msgs 한 PR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interface PR 머지, 전체 빌드 통과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRD v1.5 10.7, D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[팔레타이징] pallet_plan v1.5 (16칸 2층, 초과 처리) + S1~S8·불변식 시험</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1~S8 정답 일치, 불변식 500회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-PAL-03·04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[팔레타이징] sort_manager PALLETIZING·palletize 명령·멈춤/재개·완료 안내(실은 수·초과·경로 제외)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">게이트 기준(D3) 실기 완주</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-PAL-02·05·06·08·10·11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[팔레타이징] 음성 palletize intent (route)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palletize 5문장 중 5 정확</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-PAL-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[팔레타이징] 기록: SortResult.slot, pallet_log(미적재 포함), ListPlacements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1 기준 pallet_log 19행</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-PAL-03·09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[팔레타이징] HMI 3D 팔레트(4×2×2)·실을 수/초과/경로 제외·경고·진행률</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D 화면 재생 확인, 반영 ≤ 1초</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-PAL-10, D5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[PL] 시연 대본 v2(20개 박스, 단계 0·9), 결정 D3·D4·D6·D7, 게이트 판정·문서 갱신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대본 v2 PR, 결정 기록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRD v1.5 10.8·10.10·10.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[고도화·3순위] BoxTrack yaw 관측 + J6 회전 시 핸드아이 오차 측정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0·15·30·45° yaw 오차 기록, interface PR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-SERVO-04·06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[인계 T24] 리허설 중 검출·OCR 튜닝, 비전 이슈 1차 대응</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OCR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실패 원인 표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리허설 통과</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[고도화·3순위] 하강·들기 사다리꼴 속도 프로파일</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시뮬 통과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실기 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수준 유지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계별 시간 표</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-SERVO-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[고도화·3순위] 온라인 벨트 속도 추정 (직선 맞춤, 단계 적용)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">① 로그 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회 ② 정확도 보고 ③ 적용 여부 결정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-SERVO-02·03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[고도화·3순위] J6 회전 파지 (TRACK 초반 회전, LIFT 원위치)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계별 결과 기록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시연 장면 포함 여부 결정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-SERVO-05·07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">김학민·남현지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">팔레트 구역 좌표 교시·16칸 2층 ikin 도달성, 베이스 위치 재측정, 손가락 두께</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16칸 ikin 해 또는 대안 배치, measurements PR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-PAL-06·07, R-18~21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoveToZone PICK·DROP 2층(+27 mm)·PALLET slot 0~15·관절 경유점</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A·B·C PICK 10회, 팔레트 16칸 DROP(2층 포함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-PAL-05~07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[인계 T23·T24] 재확인 흐름 실기(흐린 송장 완주 3회), 시연 대본 운영, 리허설 진행·판정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">흐린 송장 완주 3회, 회차별 판정 기록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-OCR-06·07, NFR-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[고도화·3순위] gateway 회전 가속·각속도, 에뮬레이터 확인, 그리퍼-벨트 프레임 간섭 측정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에뮬레이터·간섭 측정 기록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-SERVO-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2-T21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1순위] A·B·C 트레이 칸 3 → 동별 7개 이상 (A·B 4×2=8, C 도달 한계 시 3×2=6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">칸별 PLACE·PICK 1회 실기, 설정·문서 PR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-PICK-08, D1, R-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파트별 진행률</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">완료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">진행</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지연</t>
+  </si>
+  <si>
+    <t xml:space="preserve">완료율 (진행률=완료)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범례: 회색 날짜 = 휴무(10/5·10/9)·주말(10/10·11, 강의실 사용 가능). 막대 색 = 파트. 출처: VOSS BRD 6.3·6.4, SRD 16장 (2026-10-05). v1.5(2026-10-12): S2-TXX = Sprint 2 작업(BRD v1.5 10장, 이슈 초안과 같은 번호, S2-T20 은 게이트), T22 를 10/11 로 당김, T23·T24 인계.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VOSS </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">마일스톤</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">날짜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마일스톤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">통과 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">관련</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인터페이스 확정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">노드·토픽·서비스 이름, intent JSON, voss_config.yaml 형식을 레포에 커밋</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SRD 9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">실측·확인 완료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">벨트 속도표, 작업대 좌표, 컨트롤러 버전, 서보 토픽 유무, RG2 경로, GPU 사양, 캘리브레이션 기록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">중간 점검 발표</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주제·진행 방향·진행률 설명 완료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정지 Pick and Place 동작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-06</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게이트</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">추종 파지 성공률 ≥ 70% (20회). 미달 시 B 개루프 동기 추종 전환 또는 범위 축소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체 루프 통합 (v1.4: 10/13 → 10/11, 남현지) · Sprint 1 마감</t>
+  </si>
+  <si>
+    <t xml:space="preserve">음성 → 판독 → 파지 → 적재 → HMI·DB 한 번에 완주</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-FN-15·20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2 게이트 (18:00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">팔레타이징 3개 동 경로 실기 1회 완주, 음성 시스템 기동 실기 1회 성공. 미달 기능은 시연 제외</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRD v1.4 10.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파트별 역할 완료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리허설 로그로 NFR-01~03 실측값 확보 (v1.4: 남현지 몫 T23·T24 인계, NFR 보고 정의석)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시연</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">박스 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계 대본 완주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 이상 올바른 구역 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ v1.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">음성 기동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·9(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">팔레타이징</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게이트 통과 시</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-NF-06, BRD 8.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">발표</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PPT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">발표 완료</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/06 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실측</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -2994,15 +3151,18 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">[Sprint 2] 시연 박스 구성: 흐린 송장 박스 동이 4개가 되는 문제 (동별 최대 3개)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제안: 동별 3개·총 9개</t>
+    <t xml:space="preserve">[Sprint 2] 시연 박스 구성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">승인(10/12): 20개 = 각 6 + 흐린 1(역삼) + 판별 불가 1(보류)</t>
   </si>
   <si>
     <t xml:space="preserve">BRD v1.4 10.10 #1</t>
   </si>
   <si>
+    <t xml:space="preserve">결정</t>
+  </si>
+  <si>
     <t xml:space="preserve">[Sprint 2] 로봇 베이스 실측 기준점과 그림 치수 차이</t>
   </si>
   <si>
@@ -3033,7 +3193,7 @@
     <t xml:space="preserve">10.10 #4</t>
   </si>
   <si>
-    <t xml:space="preserve">[Sprint 2] 팔레트 열 안 칸 피치와 놓을 때 개방 폭</t>
+    <t xml:space="preserve">[Sprint 2] 팔레트 X·Y 피치(4×2)와 놓을 때 개방 폭</t>
   </si>
   <si>
     <t xml:space="preserve">손가락 두께 실측 후</t>
@@ -3042,13 +3202,13 @@
     <t xml:space="preserve">10.10 #5</t>
   </si>
   <si>
-    <t xml:space="preserve">[Sprint 2] 팔레트 이력 음성 질의 포함 여부</t>
+    <t xml:space="preserve">[Sprint 2] 팔레타이징 이력 질의 포함 여부</t>
   </si>
   <si>
     <t xml:space="preserve">남현지, 정의석</t>
   </si>
   <si>
-    <t xml:space="preserve">Should</t>
+    <t xml:space="preserve">승인(10/12): 필수(TR-PAL-12)</t>
   </si>
   <si>
     <t xml:space="preserve">10.10 #6</t>
@@ -3060,15 +3220,12 @@
     <t xml:space="preserve">남현지(PL)</t>
   </si>
   <si>
-    <t xml:space="preserve">박병후 → 정의석 (10/12 PL 승인)</t>
+    <t xml:space="preserve">승인(10/12): 박병후 → 정의석</t>
   </si>
   <si>
     <t xml:space="preserve">10.10 #7</t>
   </si>
   <si>
-    <t xml:space="preserve">결정</t>
-  </si>
-  <si>
     <t xml:space="preserve">[Sprint 2] 추종·파지 새 사이클 목표</t>
   </si>
   <si>
@@ -3094,6 +3251,72 @@
   </si>
   <si>
     <t xml:space="preserve">10.10 #10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Sprint 2] [v1.5 D1] A·B·C 트레이 칸 수 3 → 동별 7개 이상 (C 도달 한계)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제안: A·B 4×2=8, C 3×2=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10 D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Sprint 2] [v1.5 D2] MoveToZone PALLET slot 규칙과 cols 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">남현지 작성, 김학민 리뷰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제안: slot 0~15 고정, cols 미사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10 D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Sprint 2] [v1.5 D3] 10/13 게이트 팔레타이징 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제안: 1층 8칸 완주 + 2층 1칸, 16칸은 10/14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10 D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Sprint 2] [v1.5 D4] 시연 단계 9 경로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유지 시 대치 3개 초과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10 D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Sprint 2] [v1.5 D5] 3D HMI 담당과 폴백</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제안: 늦으면 2D + 진행률</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10 D5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Sprint 2] [v1.5 D6] 같은 층 줄 순서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구현 편의, 정하면 고정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10 D6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Sprint 2] [v1.5 D7] NFR-07 20개 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제안: 20개 중 16개 이상, ADR-0012 승인 필요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10 D7</t>
   </si>
 </sst>
 </file>
@@ -3838,7 +4061,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
@@ -7423,24 +7646,24 @@
       <c r="A47" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B47" s="18" t="s">
-        <v>89</v>
+      <c r="B47" s="16" t="s">
+        <v>55</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="23" t="s">
         <v>198</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="G47" s="9" t="n">
         <f aca="false">F47-E47+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="11" t="s">
         <v>199</v>
@@ -7454,51 +7677,51 @@
       <c r="K47" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="L47" s="19" t="str">
+      <c r="L47" s="17" t="str">
         <f aca="false">IF(AND(L$4&gt;=$E47,L$4&lt;=$F47),"■","")</f>
         <v/>
       </c>
-      <c r="M47" s="19" t="str">
+      <c r="M47" s="17" t="str">
         <f aca="false">IF(AND(M$4&gt;=$E47,M$4&lt;=$F47),"■","")</f>
         <v/>
       </c>
-      <c r="N47" s="19" t="str">
+      <c r="N47" s="17" t="str">
         <f aca="false">IF(AND(N$4&gt;=$E47,N$4&lt;=$F47),"■","")</f>
         <v/>
       </c>
-      <c r="O47" s="19" t="str">
+      <c r="O47" s="17" t="str">
         <f aca="false">IF(AND(O$4&gt;=$E47,O$4&lt;=$F47),"■","")</f>
         <v/>
       </c>
-      <c r="P47" s="19" t="str">
+      <c r="P47" s="17" t="str">
         <f aca="false">IF(AND(P$4&gt;=$E47,P$4&lt;=$F47),"■","")</f>
         <v/>
       </c>
-      <c r="Q47" s="19" t="str">
+      <c r="Q47" s="17" t="str">
         <f aca="false">IF(AND(Q$4&gt;=$E47,Q$4&lt;=$F47),"■","")</f>
         <v/>
       </c>
-      <c r="R47" s="19" t="str">
+      <c r="R47" s="17" t="str">
         <f aca="false">IF(AND(R$4&gt;=$E47,R$4&lt;=$F47),"■","")</f>
-        <v>■</v>
-      </c>
-      <c r="S47" s="19" t="str">
+        <v/>
+      </c>
+      <c r="S47" s="17" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E47,S$4&lt;=$F47),"■","")</f>
         <v/>
       </c>
-      <c r="T47" s="19" t="str">
+      <c r="T47" s="17" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E47,T$4&lt;=$F47),"■","")</f>
-        <v/>
-      </c>
-      <c r="U47" s="19" t="str">
+        <v>■</v>
+      </c>
+      <c r="U47" s="17" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E47,U$4&lt;=$F47),"■","")</f>
-        <v/>
-      </c>
-      <c r="V47" s="19" t="str">
+        <v>■</v>
+      </c>
+      <c r="V47" s="17" t="str">
         <f aca="false">IF(AND(V$4&gt;=$E47,V$4&lt;=$F47),"■","")</f>
         <v/>
       </c>
-      <c r="W47" s="19" t="str">
+      <c r="W47" s="17" t="str">
         <f aca="false">IF(AND(W$4&gt;=$E47,W$4&lt;=$F47),"■","")</f>
         <v/>
       </c>
@@ -7517,14 +7740,14 @@
         <v>202</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G48" s="9" t="n">
         <f aca="false">F48-E48+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" s="11" t="s">
         <v>203</v>
@@ -7564,7 +7787,7 @@
       </c>
       <c r="R48" s="19" t="str">
         <f aca="false">IF(AND(R$4&gt;=$E48,R$4&lt;=$F48),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="S48" s="19" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E48,S$4&lt;=$F48),"■","")</f>
@@ -7572,7 +7795,7 @@
       </c>
       <c r="T48" s="19" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E48,T$4&lt;=$F48),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="U48" s="19" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E48,U$4&lt;=$F48),"■","")</f>
@@ -7685,14 +7908,14 @@
         <v>210</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F50" s="12" t="n">
         <v>46308</v>
       </c>
       <c r="G50" s="9" t="n">
         <f aca="false">F50-E50+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" s="11" t="s">
         <v>211</v>
@@ -7736,7 +7959,7 @@
       </c>
       <c r="S50" s="19" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E50,S$4&lt;=$F50),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="T50" s="19" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E50,T$4&lt;=$F50),"■","")</f>
@@ -7769,10 +7992,10 @@
         <v>214</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G51" s="9" t="n">
         <f aca="false">F51-E51+1</f>
@@ -7820,11 +8043,11 @@
       </c>
       <c r="S51" s="19" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E51,S$4&lt;=$F51),"■","")</f>
-        <v>■</v>
+        <v/>
       </c>
       <c r="T51" s="19" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E51,T$4&lt;=$F51),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="U51" s="19" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E51,U$4&lt;=$F51),"■","")</f>
@@ -7853,10 +8076,10 @@
         <v>218</v>
       </c>
       <c r="E52" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>46308</v>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>46309</v>
       </c>
       <c r="G52" s="9" t="n">
         <f aca="false">F52-E52+1</f>
@@ -7904,7 +8127,7 @@
       </c>
       <c r="S52" s="19" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E52,S$4&lt;=$F52),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="T52" s="19" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E52,T$4&lt;=$F52),"■","")</f>
@@ -7912,7 +8135,7 @@
       </c>
       <c r="U52" s="19" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E52,U$4&lt;=$F52),"■","")</f>
-        <v>■</v>
+        <v/>
       </c>
       <c r="V52" s="19" t="str">
         <f aca="false">IF(AND(V$4&gt;=$E52,V$4&lt;=$F52),"■","")</f>
@@ -7940,11 +8163,11 @@
         <v>46308</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G53" s="9" t="n">
         <f aca="false">F53-E53+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" s="11" t="s">
         <v>223</v>
@@ -7996,7 +8219,7 @@
       </c>
       <c r="U53" s="19" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E53,U$4&lt;=$F53),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="V53" s="19" t="str">
         <f aca="false">IF(AND(V$4&gt;=$E53,V$4&lt;=$F53),"■","")</f>
@@ -8024,11 +8247,11 @@
         <v>46308</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G54" s="9" t="n">
         <f aca="false">F54-E54+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" s="11" t="s">
         <v>227</v>
@@ -8080,7 +8303,7 @@
       </c>
       <c r="U54" s="19" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E54,U$4&lt;=$F54),"■","")</f>
-        <v>■</v>
+        <v/>
       </c>
       <c r="V54" s="19" t="str">
         <f aca="false">IF(AND(V$4&gt;=$E54,V$4&lt;=$F54),"■","")</f>
@@ -8095,26 +8318,26 @@
       <c r="A55" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B55" s="20" t="s">
-        <v>127</v>
+      <c r="B55" s="18" t="s">
+        <v>89</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>230</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>46309</v>
       </c>
       <c r="G55" s="9" t="n">
         <f aca="false">F55-E55+1</f>
-        <v>3</v>
-      </c>
-      <c r="H55" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H55" s="11" t="s">
         <v>231</v>
       </c>
       <c r="I55" s="9" t="s">
@@ -8126,51 +8349,51 @@
       <c r="K55" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="L55" s="21" t="str">
+      <c r="L55" s="19" t="str">
         <f aca="false">IF(AND(L$4&gt;=$E55,L$4&lt;=$F55),"■","")</f>
         <v/>
       </c>
-      <c r="M55" s="21" t="str">
+      <c r="M55" s="19" t="str">
         <f aca="false">IF(AND(M$4&gt;=$E55,M$4&lt;=$F55),"■","")</f>
         <v/>
       </c>
-      <c r="N55" s="21" t="str">
+      <c r="N55" s="19" t="str">
         <f aca="false">IF(AND(N$4&gt;=$E55,N$4&lt;=$F55),"■","")</f>
         <v/>
       </c>
-      <c r="O55" s="21" t="str">
+      <c r="O55" s="19" t="str">
         <f aca="false">IF(AND(O$4&gt;=$E55,O$4&lt;=$F55),"■","")</f>
         <v/>
       </c>
-      <c r="P55" s="21" t="str">
+      <c r="P55" s="19" t="str">
         <f aca="false">IF(AND(P$4&gt;=$E55,P$4&lt;=$F55),"■","")</f>
         <v/>
       </c>
-      <c r="Q55" s="21" t="str">
+      <c r="Q55" s="19" t="str">
         <f aca="false">IF(AND(Q$4&gt;=$E55,Q$4&lt;=$F55),"■","")</f>
         <v/>
       </c>
-      <c r="R55" s="21" t="str">
+      <c r="R55" s="19" t="str">
         <f aca="false">IF(AND(R$4&gt;=$E55,R$4&lt;=$F55),"■","")</f>
         <v/>
       </c>
-      <c r="S55" s="21" t="str">
+      <c r="S55" s="19" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E55,S$4&lt;=$F55),"■","")</f>
-        <v>■</v>
-      </c>
-      <c r="T55" s="21" t="str">
+        <v/>
+      </c>
+      <c r="T55" s="19" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E55,T$4&lt;=$F55),"■","")</f>
         <v>■</v>
       </c>
-      <c r="U55" s="21" t="str">
+      <c r="U55" s="19" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E55,U$4&lt;=$F55),"■","")</f>
         <v>■</v>
       </c>
-      <c r="V55" s="21" t="str">
+      <c r="V55" s="19" t="str">
         <f aca="false">IF(AND(V$4&gt;=$E55,V$4&lt;=$F55),"■","")</f>
         <v/>
       </c>
-      <c r="W55" s="21" t="str">
+      <c r="W55" s="19" t="str">
         <f aca="false">IF(AND(W$4&gt;=$E55,W$4&lt;=$F55),"■","")</f>
         <v/>
       </c>
@@ -8192,13 +8415,13 @@
         <v>46307</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G56" s="9" t="n">
         <f aca="false">F56-E56+1</f>
-        <v>2</v>
-      </c>
-      <c r="H56" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="H56" s="9" t="s">
         <v>235</v>
       </c>
       <c r="I56" s="9" t="s">
@@ -8248,7 +8471,7 @@
       </c>
       <c r="U56" s="21" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E56,U$4&lt;=$F56),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="V56" s="21" t="str">
         <f aca="false">IF(AND(V$4&gt;=$E56,V$4&lt;=$F56),"■","")</f>
@@ -8276,11 +8499,11 @@
         <v>46307</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G57" s="9" t="n">
         <f aca="false">F57-E57+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="23" t="s">
         <v>239</v>
@@ -8332,7 +8555,7 @@
       </c>
       <c r="U57" s="21" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E57,U$4&lt;=$F57),"■","")</f>
-        <v>■</v>
+        <v/>
       </c>
       <c r="V57" s="21" t="str">
         <f aca="false">IF(AND(V$4&gt;=$E57,V$4&lt;=$F57),"■","")</f>
@@ -8357,14 +8580,14 @@
         <v>242</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F58" s="12" t="n">
         <v>46309</v>
       </c>
       <c r="G58" s="9" t="n">
         <f aca="false">F58-E58+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" s="23" t="s">
         <v>243</v>
@@ -8408,7 +8631,7 @@
       </c>
       <c r="S58" s="21" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E58,S$4&lt;=$F58),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="T58" s="21" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E58,T$4&lt;=$F58),"■","")</f>
@@ -8431,30 +8654,30 @@
       <c r="A59" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="13" t="s">
-        <v>148</v>
+      <c r="B59" s="20" t="s">
+        <v>127</v>
       </c>
       <c r="C59" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="D59" s="11" t="s">
-        <v>247</v>
-      </c>
       <c r="E59" s="12" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="G59" s="9" t="n">
         <f aca="false">F59-E59+1</f>
-        <v>1</v>
-      </c>
-      <c r="H59" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H59" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="I59" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="J59" s="13" t="s">
         <v>29</v>
@@ -8462,77 +8685,77 @@
       <c r="K59" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="L59" s="22" t="str">
+      <c r="L59" s="21" t="str">
         <f aca="false">IF(AND(L$4&gt;=$E59,L$4&lt;=$F59),"■","")</f>
         <v/>
       </c>
-      <c r="M59" s="22" t="str">
+      <c r="M59" s="21" t="str">
         <f aca="false">IF(AND(M$4&gt;=$E59,M$4&lt;=$F59),"■","")</f>
         <v/>
       </c>
-      <c r="N59" s="22" t="str">
+      <c r="N59" s="21" t="str">
         <f aca="false">IF(AND(N$4&gt;=$E59,N$4&lt;=$F59),"■","")</f>
         <v/>
       </c>
-      <c r="O59" s="22" t="str">
+      <c r="O59" s="21" t="str">
         <f aca="false">IF(AND(O$4&gt;=$E59,O$4&lt;=$F59),"■","")</f>
         <v/>
       </c>
-      <c r="P59" s="22" t="str">
+      <c r="P59" s="21" t="str">
         <f aca="false">IF(AND(P$4&gt;=$E59,P$4&lt;=$F59),"■","")</f>
         <v/>
       </c>
-      <c r="Q59" s="22" t="str">
+      <c r="Q59" s="21" t="str">
         <f aca="false">IF(AND(Q$4&gt;=$E59,Q$4&lt;=$F59),"■","")</f>
         <v/>
       </c>
-      <c r="R59" s="22" t="str">
+      <c r="R59" s="21" t="str">
         <f aca="false">IF(AND(R$4&gt;=$E59,R$4&lt;=$F59),"■","")</f>
-        <v>■</v>
-      </c>
-      <c r="S59" s="22" t="str">
+        <v/>
+      </c>
+      <c r="S59" s="21" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E59,S$4&lt;=$F59),"■","")</f>
         <v/>
       </c>
-      <c r="T59" s="22" t="str">
+      <c r="T59" s="21" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E59,T$4&lt;=$F59),"■","")</f>
-        <v/>
-      </c>
-      <c r="U59" s="22" t="str">
+        <v>■</v>
+      </c>
+      <c r="U59" s="21" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E59,U$4&lt;=$F59),"■","")</f>
-        <v/>
-      </c>
-      <c r="V59" s="22" t="str">
+        <v>■</v>
+      </c>
+      <c r="V59" s="21" t="str">
         <f aca="false">IF(AND(V$4&gt;=$E59,V$4&lt;=$F59),"■","")</f>
         <v/>
       </c>
-      <c r="W59" s="22" t="str">
+      <c r="W59" s="21" t="str">
         <f aca="false">IF(AND(W$4&gt;=$E59,W$4&lt;=$F59),"■","")</f>
         <v/>
       </c>
     </row>
     <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>148</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>251</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G60" s="9" t="n">
         <f aca="false">F60-E60+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>252</v>
@@ -8572,7 +8795,7 @@
       </c>
       <c r="R60" s="22" t="str">
         <f aca="false">IF(AND(R$4&gt;=$E60,R$4&lt;=$F60),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="S60" s="22" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E60,S$4&lt;=$F60),"■","")</f>
@@ -8580,7 +8803,7 @@
       </c>
       <c r="T60" s="22" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E60,T$4&lt;=$F60),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="U60" s="22" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E60,U$4&lt;=$F60),"■","")</f>
@@ -8609,10 +8832,10 @@
         <v>255</v>
       </c>
       <c r="E61" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F61" s="12" t="n">
         <v>46308</v>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>46309</v>
       </c>
       <c r="G61" s="9" t="n">
         <f aca="false">F61-E61+1</f>
@@ -8660,7 +8883,7 @@
       </c>
       <c r="S61" s="22" t="str">
         <f aca="false">IF(AND(S$4&gt;=$E61,S$4&lt;=$F61),"■","")</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="T61" s="22" t="str">
         <f aca="false">IF(AND(T$4&gt;=$E61,T$4&lt;=$F61),"■","")</f>
@@ -8668,7 +8891,7 @@
       </c>
       <c r="U61" s="22" t="str">
         <f aca="false">IF(AND(U$4&gt;=$E61,U$4&lt;=$F61),"■","")</f>
-        <v>■</v>
+        <v/>
       </c>
       <c r="V61" s="22" t="str">
         <f aca="false">IF(AND(V$4&gt;=$E61,V$4&lt;=$F61),"■","")</f>
@@ -8763,188 +8986,356 @@
         <v/>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="24" t="s">
+    <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="25" t="s">
+      <c r="B63" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G63" s="9" t="n">
+        <f aca="false">F63-E63+1</f>
+        <v>2</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="J63" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="L63" s="22" t="str">
+        <f aca="false">IF(AND(L$4&gt;=$E63,L$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+      <c r="M63" s="22" t="str">
+        <f aca="false">IF(AND(M$4&gt;=$E63,M$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+      <c r="N63" s="22" t="str">
+        <f aca="false">IF(AND(N$4&gt;=$E63,N$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+      <c r="O63" s="22" t="str">
+        <f aca="false">IF(AND(O$4&gt;=$E63,O$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+      <c r="P63" s="22" t="str">
+        <f aca="false">IF(AND(P$4&gt;=$E63,P$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+      <c r="Q63" s="22" t="str">
+        <f aca="false">IF(AND(Q$4&gt;=$E63,Q$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+      <c r="R63" s="22" t="str">
+        <f aca="false">IF(AND(R$4&gt;=$E63,R$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+      <c r="S63" s="22" t="str">
+        <f aca="false">IF(AND(S$4&gt;=$E63,S$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+      <c r="T63" s="22" t="str">
+        <f aca="false">IF(AND(T$4&gt;=$E63,T$4&lt;=$F63),"■","")</f>
+        <v>■</v>
+      </c>
+      <c r="U63" s="22" t="str">
+        <f aca="false">IF(AND(U$4&gt;=$E63,U$4&lt;=$F63),"■","")</f>
+        <v>■</v>
+      </c>
+      <c r="V63" s="22" t="str">
+        <f aca="false">IF(AND(V$4&gt;=$E63,V$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+      <c r="W63" s="22" t="str">
+        <f aca="false">IF(AND(W$4&gt;=$E63,W$4&lt;=$F63),"■","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="E64" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G64" s="9" t="n">
+        <f aca="false">F64-E64+1</f>
+        <v>2</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="J64" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="L64" s="22" t="str">
+        <f aca="false">IF(AND(L$4&gt;=$E64,L$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+      <c r="M64" s="22" t="str">
+        <f aca="false">IF(AND(M$4&gt;=$E64,M$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+      <c r="N64" s="22" t="str">
+        <f aca="false">IF(AND(N$4&gt;=$E64,N$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+      <c r="O64" s="22" t="str">
+        <f aca="false">IF(AND(O$4&gt;=$E64,O$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+      <c r="P64" s="22" t="str">
+        <f aca="false">IF(AND(P$4&gt;=$E64,P$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+      <c r="Q64" s="22" t="str">
+        <f aca="false">IF(AND(Q$4&gt;=$E64,Q$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+      <c r="R64" s="22" t="str">
+        <f aca="false">IF(AND(R$4&gt;=$E64,R$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+      <c r="S64" s="22" t="str">
+        <f aca="false">IF(AND(S$4&gt;=$E64,S$4&lt;=$F64),"■","")</f>
+        <v>■</v>
+      </c>
+      <c r="T64" s="22" t="str">
+        <f aca="false">IF(AND(T$4&gt;=$E64,T$4&lt;=$F64),"■","")</f>
+        <v>■</v>
+      </c>
+      <c r="U64" s="22" t="str">
+        <f aca="false">IF(AND(U$4&gt;=$E64,U$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+      <c r="V64" s="22" t="str">
+        <f aca="false">IF(AND(V$4&gt;=$E64,V$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+      <c r="W64" s="22" t="str">
+        <f aca="false">IF(AND(W$4&gt;=$E64,W$4&lt;=$F64),"■","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="24" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C65" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="E65" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="F65" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="G65" s="25" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="26" t="s">
+      <c r="C67" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="D67" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="F67" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="G67" s="25" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C66" s="27" t="n">
-        <f aca="false">COUNTIF($B$6:$B$62,B66)</f>
-        <v>11</v>
-      </c>
-      <c r="D66" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B66,$J$6:$J$62,"완료")</f>
+      <c r="C68" s="27" t="n">
+        <f aca="false">COUNTIF($B$6:$B$64,B68)</f>
+        <v>12</v>
+      </c>
+      <c r="D68" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B68,$J$6:$J$64,"완료")</f>
         <v>0</v>
       </c>
-      <c r="E66" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B66,$J$6:$J$62,"진행")</f>
+      <c r="E68" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B68,$J$6:$J$64,"진행")</f>
         <v>0</v>
       </c>
-      <c r="F66" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B66,$J$6:$J$62,"지연")</f>
+      <c r="F68" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B68,$J$6:$J$64,"지연")</f>
         <v>0</v>
       </c>
-      <c r="G66" s="28" t="n">
-        <f aca="false">IFERROR(COUNTIFS($B$6:$B$62,B66,$K$6:$K$62,"완료")/COUNTIF($B$6:$B$62,B66),0)</f>
+      <c r="G68" s="28" t="n">
+        <f aca="false">IFERROR(COUNTIFS($B$6:$B$64,B68,$K$6:$K$64,"완료")/COUNTIF($B$6:$B$64,B68),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="29" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="C67" s="27" t="n">
-        <f aca="false">COUNTIF($B$6:$B$62,B67)</f>
+      <c r="C69" s="27" t="n">
+        <f aca="false">COUNTIF($B$6:$B$64,B69)</f>
         <v>17</v>
       </c>
-      <c r="D67" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B67,$J$6:$J$62,"완료")</f>
+      <c r="D69" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B69,$J$6:$J$64,"완료")</f>
         <v>0</v>
       </c>
-      <c r="E67" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B67,$J$6:$J$62,"진행")</f>
+      <c r="E69" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B69,$J$6:$J$64,"진행")</f>
         <v>0</v>
       </c>
-      <c r="F67" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B67,$J$6:$J$62,"지연")</f>
+      <c r="F69" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B69,$J$6:$J$64,"지연")</f>
         <v>0</v>
       </c>
-      <c r="G67" s="28" t="n">
-        <f aca="false">IFERROR(COUNTIFS($B$6:$B$62,B67,$K$6:$K$62,"완료")/COUNTIF($B$6:$B$62,B67),0)</f>
+      <c r="G69" s="28" t="n">
+        <f aca="false">IFERROR(COUNTIFS($B$6:$B$64,B69,$K$6:$K$64,"완료")/COUNTIF($B$6:$B$64,B69),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="30" t="s">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="C68" s="27" t="n">
-        <f aca="false">COUNTIF($B$6:$B$62,B68)</f>
+      <c r="C70" s="27" t="n">
+        <f aca="false">COUNTIF($B$6:$B$64,B70)</f>
         <v>9</v>
       </c>
-      <c r="D68" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B68,$J$6:$J$62,"완료")</f>
+      <c r="D70" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B70,$J$6:$J$64,"완료")</f>
         <v>0</v>
       </c>
-      <c r="E68" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B68,$J$6:$J$62,"진행")</f>
+      <c r="E70" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B70,$J$6:$J$64,"진행")</f>
         <v>0</v>
       </c>
-      <c r="F68" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B68,$J$6:$J$62,"지연")</f>
+      <c r="F70" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B70,$J$6:$J$64,"지연")</f>
         <v>0</v>
       </c>
-      <c r="G68" s="28" t="n">
-        <f aca="false">IFERROR(COUNTIFS($B$6:$B$62,B68,$K$6:$K$62,"완료")/COUNTIF($B$6:$B$62,B68),0)</f>
+      <c r="G70" s="28" t="n">
+        <f aca="false">IFERROR(COUNTIFS($B$6:$B$64,B70,$K$6:$K$64,"완료")/COUNTIF($B$6:$B$64,B70),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="31" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="C69" s="27" t="n">
-        <f aca="false">COUNTIF($B$6:$B$62,B69)</f>
-        <v>12</v>
-      </c>
-      <c r="D69" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B69,$J$6:$J$62,"완료")</f>
+      <c r="C71" s="27" t="n">
+        <f aca="false">COUNTIF($B$6:$B$64,B71)</f>
+        <v>13</v>
+      </c>
+      <c r="D71" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B71,$J$6:$J$64,"완료")</f>
         <v>0</v>
       </c>
-      <c r="E69" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B69,$J$6:$J$62,"진행")</f>
+      <c r="E71" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B71,$J$6:$J$64,"진행")</f>
         <v>0</v>
       </c>
-      <c r="F69" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B69,$J$6:$J$62,"지연")</f>
+      <c r="F71" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B71,$J$6:$J$64,"지연")</f>
         <v>0</v>
       </c>
-      <c r="G69" s="28" t="n">
-        <f aca="false">IFERROR(COUNTIFS($B$6:$B$62,B69,$K$6:$K$62,"완료")/COUNTIF($B$6:$B$62,B69),0)</f>
+      <c r="G71" s="28" t="n">
+        <f aca="false">IFERROR(COUNTIFS($B$6:$B$64,B71,$K$6:$K$64,"완료")/COUNTIF($B$6:$B$64,B71),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="32" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="27" t="n">
-        <f aca="false">COUNTIF($B$6:$B$62,B70)</f>
+      <c r="C72" s="27" t="n">
+        <f aca="false">COUNTIF($B$6:$B$64,B72)</f>
         <v>8</v>
       </c>
-      <c r="D70" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B70,$J$6:$J$62,"완료")</f>
+      <c r="D72" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B72,$J$6:$J$64,"완료")</f>
         <v>0</v>
       </c>
-      <c r="E70" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B70,$J$6:$J$62,"진행")</f>
+      <c r="E72" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B72,$J$6:$J$64,"진행")</f>
         <v>0</v>
       </c>
-      <c r="F70" s="27" t="n">
-        <f aca="false">COUNTIFS($B$6:$B$62,B70,$J$6:$J$62,"지연")</f>
+      <c r="F72" s="27" t="n">
+        <f aca="false">COUNTIFS($B$6:$B$64,B72,$J$6:$J$64,"지연")</f>
         <v>0</v>
       </c>
-      <c r="G70" s="28" t="n">
-        <f aca="false">IFERROR(COUNTIFS($B$6:$B$62,B70,$K$6:$K$62,"완료")/COUNTIF($B$6:$B$62,B70),0)</f>
+      <c r="G72" s="28" t="n">
+        <f aca="false">IFERROR(COUNTIFS($B$6:$B$64,B72,$K$6:$K$64,"완료")/COUNTIF($B$6:$B$64,B72),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="33" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C71" s="33" t="n">
-        <f aca="false">COUNTA($A$6:$A$62)</f>
-        <v>57</v>
-      </c>
-      <c r="D71" s="33" t="n">
-        <f aca="false">COUNTIF($J$6:$J$62,"완료")</f>
+      <c r="C73" s="33" t="n">
+        <f aca="false">COUNTA($A$6:$A$64)</f>
+        <v>59</v>
+      </c>
+      <c r="D73" s="33" t="n">
+        <f aca="false">COUNTIF($J$6:$J$64,"완료")</f>
         <v>0</v>
       </c>
-      <c r="E71" s="33" t="n">
-        <f aca="false">COUNTIF($J$6:$J$62,"진행")</f>
+      <c r="E73" s="33" t="n">
+        <f aca="false">COUNTIF($J$6:$J$64,"진행")</f>
         <v>0</v>
       </c>
-      <c r="F71" s="33" t="n">
-        <f aca="false">COUNTIF($J$6:$J$62,"지연")</f>
+      <c r="F73" s="33" t="n">
+        <f aca="false">COUNTIF($J$6:$J$64,"지연")</f>
         <v>0</v>
       </c>
-      <c r="G71" s="34" t="n">
-        <f aca="false">IFERROR(COUNTIF($K$6:$K$62,"완료")/COUNTA($A$6:$A$62),0)</f>
+      <c r="G73" s="34" t="n">
+        <f aca="false">IFERROR(COUNTIF($K$6:$K$64,"완료")/COUNTA($A$6:$A$64),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="35" t="s">
-        <v>268</v>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="35" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L6:W62">
+  <conditionalFormatting sqref="L6:W64">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(L6="■",$B6="음성·웹·HMI")</formula>
     </cfRule>
@@ -8962,11 +9353,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J6:J62" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J6:J64" type="list">
       <formula1>"예정,진행,완료,지연"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="시작전, 진행중, 완료 중에서 고르세요" errorStyle="stop" errorTitle="진행률" operator="between" prompt="▼를 눌러 시작전·진행중·완료 중 선택" promptTitle="진행률" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K6:K62" type="list">
+    <dataValidation allowBlank="true" error="시작전, 진행중, 완료 중에서 고르세요" errorStyle="stop" errorTitle="진행률" operator="between" prompt="▼를 눌러 시작전·진행중·완료 중 선택" promptTitle="진행률" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K6:K64" type="list">
       <formula1>"시작전,진행중,완료"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8998,21 +9389,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>11</v>
@@ -9023,13 +9414,13 @@
         <v>46300</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>29</v>
@@ -9040,10 +9431,10 @@
         <v>46301</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>34</v>
@@ -9057,10 +9448,10 @@
         <v>46302</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>38</v>
@@ -9074,13 +9465,13 @@
         <v>46303</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>171</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>29</v>
@@ -9091,10 +9482,10 @@
         <v>46305</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>42</v>
@@ -9108,13 +9499,13 @@
         <v>46306</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>29</v>
@@ -9125,13 +9516,13 @@
         <v>46308</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>183</v>
+        <v>298</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>29</v>
@@ -9142,10 +9533,10 @@
         <v>46309</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>38</v>
@@ -9159,13 +9550,13 @@
         <v>46310</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>29</v>
@@ -9176,10 +9567,10 @@
         <v>46311</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>53</v>
@@ -9223,27 +9614,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="37" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C2" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9251,17 +9642,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>149</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="9" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9269,17 +9660,17 @@
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>149</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="9" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9287,17 +9678,17 @@
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>128</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="9" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9305,7 +9696,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>149</v>
@@ -9315,7 +9706,7 @@
         <v>168</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9323,17 +9714,17 @@
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>56</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="9" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9341,17 +9732,17 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>149</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" s="38" t="s">
         <v>313</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9359,7 +9750,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>90</v>
@@ -9369,7 +9760,7 @@
         <v>93</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9377,17 +9768,17 @@
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>149</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="9" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9395,17 +9786,17 @@
         <v>9</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>149</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9413,17 +9804,17 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>56</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="9" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9454,7 +9845,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -9468,27 +9859,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="37" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C2" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>11</v>
@@ -9499,7 +9890,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>25</v>
@@ -9509,10 +9900,10 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9520,7 +9911,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>56</v>
@@ -9530,10 +9921,10 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9541,7 +9932,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>56</v>
@@ -9551,10 +9942,10 @@
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9562,7 +9953,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>56</v>
@@ -9575,7 +9966,7 @@
         <v>67</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9583,7 +9974,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>90</v>
@@ -9593,10 +9984,10 @@
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="9" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9604,7 +9995,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>56</v>
@@ -9614,10 +10005,10 @@
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>335</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9625,7 +10016,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>56</v>
@@ -9635,10 +10026,10 @@
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="9" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9646,7 +10037,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>149</v>
@@ -9656,10 +10047,10 @@
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="9" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9667,7 +10058,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>149</v>
@@ -9677,10 +10068,10 @@
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="9" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9688,7 +10079,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>25</v>
@@ -9698,10 +10089,10 @@
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="9" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9709,7 +10100,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>25</v>
@@ -9722,7 +10113,7 @@
         <v>53</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9730,7 +10121,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>25</v>
@@ -9743,7 +10134,7 @@
         <v>135</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9751,7 +10142,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>25</v>
@@ -9761,10 +10152,10 @@
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="9" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9772,22 +10163,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>326</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9795,7 +10186,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>149</v>
@@ -9804,13 +10195,13 @@
         <v>46306</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9818,22 +10209,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="D18" s="40" t="n">
         <v>46306</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9841,7 +10232,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>56</v>
@@ -9850,13 +10241,13 @@
         <v>46307</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9864,22 +10255,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>149</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9887,22 +10278,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>326</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9910,22 +10301,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="D22" s="40" t="n">
         <v>46307</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9933,7 +10324,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>25</v>
@@ -9942,13 +10333,13 @@
         <v>46309</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9956,7 +10347,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>128</v>
@@ -9965,13 +10356,13 @@
         <v>46309</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9979,7 +10370,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>128</v>
@@ -9988,24 +10379,185 @@
         <v>46307</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11" t="str">
-        <f aca="false">"결정 "&amp;COUNTIF(G3:G25,"결정")&amp;" / "&amp;COUNTA(B3:B25)</f>
-        <v>결정 1 / 23</v>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="40" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D27" s="40" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="40" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="40" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D30" s="40" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="40" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="40" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="11" t="str">
+        <f aca="false">"결정 "&amp;COUNTIF(G3:G32,"결정")&amp;" / "&amp;COUNTA(B3:B32)</f>
+        <v>결정 3 / 30</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G3:G25" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G3:G32" type="list">
       <formula1>"미정,결정"</formula1>
       <formula2>0</formula2>
     </dataValidation>
